--- a/exports/trend_1d/PRESTIGE_full_report.xlsx
+++ b/exports/trend_1d/PRESTIGE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>15.6</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H2" t="n">
-        <v>253.8</v>
+        <v>243.05</v>
       </c>
       <c r="I2" t="n">
         <v>249.0746691314652</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K2" t="n">
-        <v>3.15</v>
+        <v>-1.22</v>
       </c>
       <c r="L2" t="n">
         <v>9.710000000000001</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>17.1</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42132</v>
+        <v>42135</v>
       </c>
       <c r="H3" t="n">
-        <v>261.45</v>
+        <v>279.6</v>
       </c>
       <c r="I3" t="n">
         <v>273.3037910041237</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.57</v>
+        <v>-15.04</v>
       </c>
       <c r="L3" t="n">
-        <v>10.24</v>
+        <v>20.63</v>
       </c>
       <c r="M3" t="n">
         <v>3.27</v>
       </c>
       <c r="N3" t="n">
-        <v>5.17</v>
+        <v>6.94</v>
       </c>
       <c r="O3" t="n">
         <v>-4.24</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>17.4</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42200</v>
+        <v>42201</v>
       </c>
       <c r="H4" t="n">
-        <v>240</v>
+        <v>237.3</v>
       </c>
       <c r="I4" t="n">
         <v>237.5636360181991</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K4" t="n">
-        <v>-14.16</v>
+        <v>-15.13</v>
       </c>
       <c r="L4" t="n">
         <v>16.67</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.32</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42291</v>
+        <v>42292</v>
       </c>
       <c r="H5" t="n">
-        <v>213.25</v>
+        <v>218</v>
       </c>
       <c r="I5" t="n">
         <v>217.2730380170314</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K5" t="n">
-        <v>10.13</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>2.04</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>10.96</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42314</v>
+        <v>42317</v>
       </c>
       <c r="H6" t="n">
-        <v>198.8</v>
+        <v>194.8</v>
       </c>
       <c r="I6" t="n">
         <v>195.552516201363</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.81</v>
+        <v>-10.64</v>
       </c>
       <c r="L6" t="n">
-        <v>10.05</v>
+        <v>11.38</v>
       </c>
       <c r="M6" t="n">
         <v>0.31</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>10.56</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42339</v>
+        <v>42340</v>
       </c>
       <c r="H7" t="n">
-        <v>204.1</v>
+        <v>215.05</v>
       </c>
       <c r="I7" t="n">
         <v>210.3966846856907</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.77</v>
+        <v>-10.4</v>
       </c>
       <c r="L7" t="n">
-        <v>6.78</v>
+        <v>15.43</v>
       </c>
       <c r="M7" t="n">
         <v>2.41</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>11.92</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42370</v>
+        <v>42373</v>
       </c>
       <c r="H8" t="n">
-        <v>194.8</v>
+        <v>190.45</v>
       </c>
       <c r="I8" t="n">
         <v>192.1765091602769</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.42</v>
+        <v>-11.44</v>
       </c>
       <c r="L8" t="n">
-        <v>10.63</v>
+        <v>12.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.4</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>11.59</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42450</v>
+        <v>42451</v>
       </c>
       <c r="H9" t="n">
-        <v>153.2</v>
+        <v>159.6</v>
       </c>
       <c r="I9" t="n">
         <v>155.399845795638</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K9" t="n">
-        <v>19.56</v>
+        <v>16.2</v>
       </c>
       <c r="L9" t="n">
         <v>3.91</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>18.21</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42611</v>
+        <v>42612</v>
       </c>
       <c r="H10" t="n">
-        <v>179.9</v>
+        <v>176.35</v>
       </c>
       <c r="I10" t="n">
         <v>179.7323620149983</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K10" t="n">
-        <v>12.72</v>
+        <v>10.49</v>
       </c>
       <c r="L10" t="n">
         <v>5.86</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>12.76</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42615</v>
+        <v>42619</v>
       </c>
       <c r="H11" t="n">
-        <v>185.65</v>
+        <v>202.45</v>
       </c>
       <c r="I11" t="n">
         <v>198.8520718397181</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.27</v>
+        <v>-14.8</v>
       </c>
       <c r="L11" t="n">
-        <v>7.74</v>
+        <v>15.96</v>
       </c>
       <c r="M11" t="n">
-        <v>0.22</v>
+        <v>2.29</v>
       </c>
       <c r="N11" t="n">
-        <v>5.5</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>-1.97</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>15.75</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42677</v>
+        <v>42678</v>
       </c>
       <c r="H12" t="n">
-        <v>186.75</v>
+        <v>181.3</v>
       </c>
       <c r="I12" t="n">
         <v>181.8146895954767</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K12" t="n">
-        <v>-7.76</v>
+        <v>-10.45</v>
       </c>
       <c r="L12" t="n">
         <v>10.99</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>14.29</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42718</v>
+        <v>42719</v>
       </c>
       <c r="H13" t="n">
-        <v>163.75</v>
+        <v>167.95</v>
       </c>
       <c r="I13" t="n">
         <v>166.6741523100025</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K13" t="n">
-        <v>9.68</v>
+        <v>7.36</v>
       </c>
       <c r="L13" t="n">
         <v>4.52</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>15.49</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42877</v>
+        <v>42878</v>
       </c>
       <c r="H14" t="n">
-        <v>235.5</v>
+        <v>227.95</v>
       </c>
       <c r="I14" t="n">
         <v>230.1605186231792</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K14" t="n">
-        <v>40.22</v>
+        <v>35.72</v>
       </c>
       <c r="L14" t="n">
         <v>7.14</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>15.72</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42899</v>
+        <v>42900</v>
       </c>
       <c r="H15" t="n">
-        <v>254.5</v>
+        <v>264.9</v>
       </c>
       <c r="I15" t="n">
         <v>256.9546145151705</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K15" t="n">
-        <v>-11.65</v>
+        <v>-16.21</v>
       </c>
       <c r="L15" t="n">
-        <v>13.62</v>
+        <v>17.35</v>
       </c>
       <c r="M15" t="n">
         <v>3.67</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,25 +1523,25 @@
         <v>13.86</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43136</v>
+        <v>43137</v>
       </c>
       <c r="H16" t="n">
-        <v>302.25</v>
+        <v>288.45</v>
       </c>
       <c r="I16" t="n">
         <v>301.095177729443</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K16" t="n">
-        <v>14.1</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L16" t="n">
         <v>11.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.13</v>
+        <v>4.12</v>
       </c>
       <c r="N16" t="n">
         <v>5.62</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>161</v>
+        <v>162</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>9</v>
+      </c>
+      <c r="U16" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>15.94</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43158</v>
+        <v>43159</v>
       </c>
       <c r="H17" t="n">
-        <v>325.05</v>
+        <v>335.3</v>
       </c>
       <c r="I17" t="n">
         <v>334.4155390561679</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>-12.69</v>
+        <v>-16.24</v>
       </c>
       <c r="L17" t="n">
-        <v>18.77</v>
+        <v>18.96</v>
       </c>
       <c r="M17" t="n">
         <v>4.24</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>16.05</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43181</v>
+        <v>43182</v>
       </c>
       <c r="H18" t="n">
-        <v>288.7</v>
+        <v>279.3</v>
       </c>
       <c r="I18" t="n">
         <v>283.7871119495408</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K18" t="n">
-        <v>-13.9</v>
+        <v>-16.7</v>
       </c>
       <c r="L18" t="n">
-        <v>15.46</v>
+        <v>20</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>2.53</v>
       </c>
       <c r="N18" t="n">
         <v>5.22</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>14.13</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43264</v>
+        <v>43265</v>
       </c>
       <c r="H19" t="n">
-        <v>264.1</v>
+        <v>274.95</v>
       </c>
       <c r="I19" t="n">
         <v>266.6995478030423</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K19" t="n">
-        <v>5.44</v>
+        <v>1.56</v>
       </c>
       <c r="L19" t="n">
         <v>13.73</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>14.28</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43339</v>
+        <v>43340</v>
       </c>
       <c r="H20" t="n">
-        <v>246.15</v>
+        <v>240.25</v>
       </c>
       <c r="I20" t="n">
         <v>243.849602191903</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K20" t="n">
-        <v>-10.47</v>
+        <v>-12.62</v>
       </c>
       <c r="L20" t="n">
-        <v>12.64</v>
+        <v>13.51</v>
       </c>
       <c r="M20" t="n">
         <v>1.75</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.9</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43432</v>
+        <v>43433</v>
       </c>
       <c r="H21" t="n">
-        <v>183.2</v>
+        <v>198.35</v>
       </c>
       <c r="I21" t="n">
         <v>192.7928529942828</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K21" t="n">
-        <v>23.75</v>
+        <v>17.44</v>
       </c>
       <c r="L21" t="n">
         <v>3.52</v>
@@ -1638,7 +1889,7 @@
         <v>2.77</v>
       </c>
       <c r="N21" t="n">
-        <v>7.57</v>
+        <v>8.27</v>
       </c>
       <c r="O21" t="n">
         <v>-2.4</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>15.9</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H22" t="n">
-        <v>206.25</v>
+        <v>203.9</v>
       </c>
       <c r="I22" t="n">
         <v>205.2469893888347</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K22" t="n">
-        <v>3.98</v>
+        <v>2.8</v>
       </c>
       <c r="L22" t="n">
         <v>8.140000000000001</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>14.73</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43538</v>
+        <v>43539</v>
       </c>
       <c r="H23" t="n">
-        <v>211.5</v>
+        <v>215.6</v>
       </c>
       <c r="I23" t="n">
         <v>213.0202551314255</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.73</v>
+        <v>-5.74</v>
       </c>
       <c r="L23" t="n">
         <v>8.779999999999999</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.85</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43595</v>
+        <v>43598</v>
       </c>
       <c r="H24" t="n">
-        <v>264.2</v>
+        <v>244.4</v>
       </c>
       <c r="I24" t="n">
         <v>249.1517092067862</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K24" t="n">
-        <v>22.54</v>
+        <v>13.36</v>
       </c>
       <c r="L24" t="n">
         <v>1.76</v>
@@ -1809,7 +2096,7 @@
         <v>2.01</v>
       </c>
       <c r="N24" t="n">
-        <v>5.14</v>
+        <v>7.49</v>
       </c>
       <c r="O24" t="n">
         <v>1.94</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>16.07</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H25" t="n">
-        <v>264.7</v>
+        <v>280.6</v>
       </c>
       <c r="I25" t="n">
         <v>272.1055771969469</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>-8.31</v>
+        <v>-14.81</v>
       </c>
       <c r="L25" t="n">
-        <v>10.43</v>
+        <v>15.51</v>
       </c>
       <c r="M25" t="n">
         <v>2.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.27</v>
+        <v>6.01</v>
       </c>
       <c r="O25" t="n">
         <v>-7.49</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>14.05</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H26" t="n">
-        <v>274.5</v>
+        <v>257</v>
       </c>
       <c r="I26" t="n">
         <v>260.4886584825066</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.17</v>
+        <v>-8.41</v>
       </c>
       <c r="L26" t="n">
-        <v>8.449999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="M26" t="n">
         <v>1.99</v>
       </c>
       <c r="N26" t="n">
-        <v>5.11</v>
+        <v>6.38</v>
       </c>
       <c r="O26" t="n">
         <v>6.01</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>19.69</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43684</v>
+        <v>43685</v>
       </c>
       <c r="H27" t="n">
-        <v>278.8</v>
+        <v>287.5</v>
       </c>
       <c r="I27" t="n">
         <v>286.689176612709</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K27" t="n">
-        <v>-8.48</v>
+        <v>-11.87</v>
       </c>
       <c r="L27" t="n">
-        <v>12.06</v>
+        <v>12.41</v>
       </c>
       <c r="M27" t="n">
         <v>1.16</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>14.34</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43724</v>
+        <v>43725</v>
       </c>
       <c r="H28" t="n">
-        <v>300.3</v>
+        <v>275.75</v>
       </c>
       <c r="I28" t="n">
         <v>278.1420643999721</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>4.45</v>
+        <v>-4.09</v>
       </c>
       <c r="L28" t="n">
-        <v>3.97</v>
+        <v>4.85</v>
       </c>
       <c r="M28" t="n">
         <v>2.52</v>
       </c>
       <c r="N28" t="n">
-        <v>2.97</v>
+        <v>8.18</v>
       </c>
       <c r="O28" t="n">
         <v>3.12</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>18.36</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43798</v>
+        <v>43801</v>
       </c>
       <c r="H29" t="n">
-        <v>303.8</v>
+        <v>322.9</v>
       </c>
       <c r="I29" t="n">
         <v>317.7298798413412</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K29" t="n">
-        <v>-10.17</v>
+        <v>-17.1</v>
       </c>
       <c r="L29" t="n">
         <v>23.23</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>17.79</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43886</v>
+        <v>43887</v>
       </c>
       <c r="H30" t="n">
-        <v>340.5</v>
+        <v>333.6</v>
       </c>
       <c r="I30" t="n">
         <v>338.9181745585614</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K30" t="n">
-        <v>5.45</v>
+        <v>3.31</v>
       </c>
       <c r="L30" t="n">
         <v>7.71</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>16.48</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43984</v>
+        <v>43985</v>
       </c>
       <c r="H31" t="n">
-        <v>165.1</v>
+        <v>169.15</v>
       </c>
       <c r="I31" t="n">
         <v>166.5227691724705</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K31" t="n">
-        <v>50.51</v>
+        <v>49.3</v>
       </c>
       <c r="L31" t="n">
         <v>2.68</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>18.03</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44025</v>
+        <v>44026</v>
       </c>
       <c r="H32" t="n">
-        <v>189.15</v>
+        <v>185.5</v>
       </c>
       <c r="I32" t="n">
         <v>186.8645590976226</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K32" t="n">
-        <v>11.82</v>
+        <v>9.67</v>
       </c>
       <c r="L32" t="n">
         <v>4.52</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>19.63</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44047</v>
+        <v>44048</v>
       </c>
       <c r="H33" t="n">
-        <v>202.6</v>
+        <v>203.85</v>
       </c>
       <c r="I33" t="n">
         <v>203.671084298747</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K33" t="n">
-        <v>-9.220000000000001</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="L33" t="n">
         <v>11.97</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>13.94</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44186</v>
+        <v>44187</v>
       </c>
       <c r="H34" t="n">
-        <v>267.35</v>
+        <v>255.55</v>
       </c>
       <c r="I34" t="n">
         <v>263.725758184643</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K34" t="n">
-        <v>31.15</v>
+        <v>25.36</v>
       </c>
       <c r="L34" t="n">
         <v>1.3</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>15.15</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44207</v>
+        <v>44208</v>
       </c>
       <c r="H35" t="n">
-        <v>290.95</v>
+        <v>296.55</v>
       </c>
       <c r="I35" t="n">
         <v>294.2763315736598</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K35" t="n">
-        <v>-13.85</v>
+        <v>-16.04</v>
       </c>
       <c r="L35" t="n">
-        <v>14.85</v>
+        <v>19.39</v>
       </c>
       <c r="M35" t="n">
         <v>2.7</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>11.26</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44305</v>
+        <v>44306</v>
       </c>
       <c r="H36" t="n">
-        <v>278.65</v>
+        <v>275.1</v>
       </c>
       <c r="I36" t="n">
         <v>275.4574239046129</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K36" t="n">
-        <v>-6.04</v>
+        <v>-7.23</v>
       </c>
       <c r="L36" t="n">
         <v>10.3</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>18.4</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44354</v>
+        <v>44355</v>
       </c>
       <c r="H37" t="n">
-        <v>288.1</v>
+        <v>291.55</v>
       </c>
       <c r="I37" t="n">
         <v>289.5436785710163</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.73</v>
+        <v>-5.98</v>
       </c>
       <c r="L37" t="n">
         <v>7.49</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.53</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44428</v>
+        <v>44431</v>
       </c>
       <c r="H38" t="n">
-        <v>331.95</v>
+        <v>324</v>
       </c>
       <c r="I38" t="n">
         <v>325.5525469220815</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K38" t="n">
-        <v>13.86</v>
+        <v>11.13</v>
       </c>
       <c r="L38" t="n">
         <v>6.02</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>16.67</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44440</v>
+        <v>44441</v>
       </c>
       <c r="H39" t="n">
-        <v>372.25</v>
+        <v>383.15</v>
       </c>
       <c r="I39" t="n">
         <v>378.0217723259798</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K39" t="n">
-        <v>-14.89</v>
+        <v>-18.26</v>
       </c>
       <c r="L39" t="n">
-        <v>18.32</v>
+        <v>19.26</v>
       </c>
       <c r="M39" t="n">
         <v>1.05</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>15.34</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44523</v>
+        <v>44524</v>
       </c>
       <c r="H40" t="n">
-        <v>441.2</v>
+        <v>435.85</v>
       </c>
       <c r="I40" t="n">
         <v>436.0939740638672</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K40" t="n">
-        <v>15.15</v>
+        <v>13.75</v>
       </c>
       <c r="L40" t="n">
         <v>5.01</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>17.86</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44574</v>
+        <v>44575</v>
       </c>
       <c r="H41" t="n">
-        <v>491.4</v>
+        <v>504.45</v>
       </c>
       <c r="I41" t="n">
         <v>502.6244776671642</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K41" t="n">
-        <v>-12.75</v>
+        <v>-15.74</v>
       </c>
       <c r="L41" t="n">
-        <v>15.1</v>
+        <v>17.01</v>
       </c>
       <c r="M41" t="n">
         <v>1.51</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>14.75</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44596</v>
+        <v>44599</v>
       </c>
       <c r="H42" t="n">
-        <v>469.95</v>
+        <v>458.25</v>
       </c>
       <c r="I42" t="n">
         <v>466.5627315778809</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>-6.84</v>
+        <v>-9.16</v>
       </c>
       <c r="L42" t="n">
         <v>10.51</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>16.33</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H43" t="n">
-        <v>459.8</v>
+        <v>483.2</v>
       </c>
       <c r="I43" t="n">
         <v>467.563336306404</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.34</v>
+        <v>-5.44</v>
       </c>
       <c r="L43" t="n">
-        <v>3.4</v>
+        <v>6.06</v>
       </c>
       <c r="M43" t="n">
         <v>1.87</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>15.52</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44690</v>
+        <v>44691</v>
       </c>
       <c r="H44" t="n">
-        <v>446.6</v>
+        <v>441.3</v>
       </c>
       <c r="I44" t="n">
         <v>443.4409614601706</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K44" t="n">
-        <v>-7.57</v>
+        <v>-8.67</v>
       </c>
       <c r="L44" t="n">
-        <v>8.83</v>
+        <v>9.77</v>
       </c>
       <c r="M44" t="n">
         <v>1.92</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.98</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44754</v>
+        <v>44755</v>
       </c>
       <c r="H45" t="n">
-        <v>432.15</v>
+        <v>437.75</v>
       </c>
       <c r="I45" t="n">
         <v>433.6884189179301</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K45" t="n">
-        <v>2.07</v>
+        <v>0.8</v>
       </c>
       <c r="L45" t="n">
         <v>4.04</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>12.74</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H46" t="n">
-        <v>449.85</v>
+        <v>434.3</v>
       </c>
       <c r="I46" t="n">
         <v>439.9411377754863</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K46" t="n">
-        <v>2.76</v>
+        <v>-0.79</v>
       </c>
       <c r="L46" t="n">
         <v>5.88</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>12.77</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44880</v>
+        <v>44881</v>
       </c>
       <c r="H47" t="n">
-        <v>462.35</v>
+        <v>475.4</v>
       </c>
       <c r="I47" t="n">
         <v>475.2329380653179</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.46</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L47" t="n">
         <v>11.67</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>10.65</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H48" t="n">
-        <v>452.9</v>
+        <v>451.05</v>
       </c>
       <c r="I48" t="n">
         <v>452.4861823766132</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.73</v>
+        <v>-5.12</v>
       </c>
       <c r="L48" t="n">
-        <v>5.23</v>
+        <v>7.36</v>
       </c>
       <c r="M48" t="n">
         <v>1.57</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>10.97</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44974</v>
+        <v>44977</v>
       </c>
       <c r="H49" t="n">
-        <v>433.25</v>
+        <v>437.35</v>
       </c>
       <c r="I49" t="n">
         <v>436.2095095181207</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K49" t="n">
-        <v>3.95</v>
+        <v>3.04</v>
       </c>
       <c r="L49" t="n">
         <v>5.3</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>10.78</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H50" t="n">
-        <v>1286.7</v>
+        <v>1136.45</v>
       </c>
       <c r="I50" t="n">
         <v>1189.88949692385</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K50" t="n">
-        <v>194.2</v>
+        <v>159.85</v>
       </c>
       <c r="L50" t="n">
         <v>10.6</v>
@@ -3291,7 +3890,7 @@
         <v>3.88</v>
       </c>
       <c r="N50" t="n">
-        <v>6.39</v>
+        <v>11.68</v>
       </c>
       <c r="O50" t="n">
         <v>0.95</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>228</v>
+        <v>229</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>12</v>
+      </c>
+      <c r="U50" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>27.44</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="H51" t="n">
-        <v>1150.2</v>
+        <v>1190.75</v>
       </c>
       <c r="I51" t="n">
         <v>1175.754283864323</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.21</v>
+        <v>-4.78</v>
       </c>
       <c r="L51" t="n">
         <v>14.65</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>16.33</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H52" t="n">
-        <v>1695.75</v>
+        <v>1623.45</v>
       </c>
       <c r="I52" t="n">
         <v>1671.379778680633</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K52" t="n">
-        <v>42.41</v>
+        <v>36.34</v>
       </c>
       <c r="L52" t="n">
         <v>4.59</v>
       </c>
       <c r="M52" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="N52" t="n">
         <v>12.88</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>6</v>
+      </c>
+      <c r="U52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>16.88</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45551</v>
+        <v>45552</v>
       </c>
       <c r="H53" t="n">
-        <v>1834.9</v>
+        <v>1917.4</v>
       </c>
       <c r="I53" t="n">
         <v>1897.420690629484</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K53" t="n">
-        <v>-13.02</v>
+        <v>-18.11</v>
       </c>
       <c r="L53" t="n">
-        <v>18.23</v>
+        <v>21.47</v>
       </c>
       <c r="M53" t="n">
         <v>4.41</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>16.54</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45590</v>
+        <v>45593</v>
       </c>
       <c r="H54" t="n">
-        <v>1706.95</v>
+        <v>1655.25</v>
       </c>
       <c r="I54" t="n">
         <v>1665.388617819262</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K54" t="n">
-        <v>-10.98</v>
+        <v>-13.67</v>
       </c>
       <c r="L54" t="n">
         <v>14.2</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>13.68</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="H55" t="n">
-        <v>1724.15</v>
+        <v>1770.55</v>
       </c>
       <c r="I55" t="n">
         <v>1749.503724926498</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.16</v>
+        <v>-6.97</v>
       </c>
       <c r="L55" t="n">
-        <v>6.03</v>
+        <v>7.49</v>
       </c>
       <c r="M55" t="n">
         <v>2.08</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>13.44</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="H56" t="n">
-        <v>1752.5</v>
+        <v>1675</v>
       </c>
       <c r="I56" t="n">
         <v>1688.296407529321</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.02</v>
+        <v>-5.4</v>
       </c>
       <c r="L56" t="n">
-        <v>4.07</v>
+        <v>6.7</v>
       </c>
       <c r="M56" t="n">
         <v>1.81</v>
       </c>
       <c r="N56" t="n">
-        <v>3.72</v>
+        <v>4.42</v>
       </c>
       <c r="O56" t="n">
         <v>2.69</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>14.28</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H57" t="n">
-        <v>1359.5</v>
+        <v>1431.7</v>
       </c>
       <c r="I57" t="n">
         <v>1430.633933746713</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K57" t="n">
-        <v>18.84</v>
+        <v>14.53</v>
       </c>
       <c r="L57" t="n">
         <v>5.92</v>
@@ -3690,7 +4373,7 @@
         <v>1.27</v>
       </c>
       <c r="N57" t="n">
-        <v>3.72</v>
+        <v>5.31</v>
       </c>
       <c r="O57" t="n">
         <v>-4.42</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>16.25</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45709</v>
+        <v>45712</v>
       </c>
       <c r="H58" t="n">
-        <v>1216.3</v>
+        <v>1186.1</v>
       </c>
       <c r="I58" t="n">
         <v>1201.752316681642</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K58" t="n">
-        <v>-15.05</v>
+        <v>-17.15</v>
       </c>
       <c r="L58" t="n">
-        <v>17.2</v>
+        <v>18.98</v>
       </c>
       <c r="M58" t="n">
         <v>2.29</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>15.15</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H59" t="n">
-        <v>1215.2</v>
+        <v>1268.6</v>
       </c>
       <c r="I59" t="n">
         <v>1233.736322410188</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.45</v>
+        <v>-6.96</v>
       </c>
       <c r="L59" t="n">
-        <v>7.24</v>
+        <v>7.45</v>
       </c>
       <c r="M59" t="n">
         <v>4.5</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>14.81</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H60" t="n">
-        <v>1669.1</v>
+        <v>1611.3</v>
       </c>
       <c r="I60" t="n">
         <v>1659.25207963955</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K60" t="n">
-        <v>31.57</v>
+        <v>27.01</v>
       </c>
       <c r="L60" t="n">
         <v>4.82</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>10.49</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="H61" t="n">
-        <v>1603.6</v>
+        <v>1676</v>
       </c>
       <c r="I61" t="n">
         <v>1638.403732298239</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K61" t="n">
-        <v>0.48</v>
+        <v>-4.02</v>
       </c>
       <c r="L61" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="M61" t="n">
         <v>3.71</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>11.14</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="H62" t="n">
-        <v>1688.5</v>
+        <v>1631.3</v>
       </c>
       <c r="I62" t="n">
         <v>1640.126499829943</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K62" t="n">
-        <v>0.75</v>
+        <v>-2.67</v>
       </c>
       <c r="L62" t="n">
         <v>4.93</v>
@@ -3975,7 +4718,7 @@
         <v>0.95</v>
       </c>
       <c r="N62" t="n">
-        <v>3.26</v>
+        <v>3.39</v>
       </c>
       <c r="O62" t="n">
         <v>4.51</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>11.61</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H63" t="n">
-        <v>1483.2</v>
+        <v>1543.3</v>
       </c>
       <c r="I63" t="n">
         <v>1531.884385034913</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K63" t="n">
-        <v>9.08</v>
+        <v>5.39</v>
       </c>
       <c r="L63" t="n">
         <v>4.94</v>
       </c>
       <c r="M63" t="n">
-        <v>0.99</v>
+        <v>4.5</v>
       </c>
       <c r="N63" t="n">
-        <v>2.98</v>
+        <v>4.05</v>
       </c>
       <c r="O63" t="n">
         <v>-3.39</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>12.36</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="H64" t="n">
-        <v>1425.6</v>
+        <v>1420.7</v>
       </c>
       <c r="I64" t="n">
         <v>1422.146249886482</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.63</v>
+        <v>-7.94</v>
       </c>
       <c r="L64" t="n">
         <v>8.74</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>12.33</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H65" t="n">
-        <v>1222.1</v>
+        <v>1320.8</v>
       </c>
       <c r="I65" t="n">
         <v>1288.887950686882</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K65" t="n">
-        <v>13.98</v>
+        <v>7.03</v>
       </c>
       <c r="L65" t="n">
         <v>3.36</v>
       </c>
       <c r="M65" t="n">
-        <v>2.47</v>
+        <v>6.37</v>
       </c>
       <c r="N65" t="n">
-        <v>4.39</v>
+        <v>8.08</v>
       </c>
       <c r="O65" t="n">
         <v>-0.34</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>14.88</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="H66" t="n">
-        <v>1369.8</v>
+        <v>1342.2</v>
       </c>
       <c r="I66" t="n">
         <v>1360.425439813886</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K66" t="n">
-        <v>3.71</v>
+        <v>1.62</v>
       </c>
       <c r="L66" t="n">
         <v>4.53</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>12.37</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="H67" t="n">
-        <v>1387.3</v>
+        <v>1472.5</v>
       </c>
       <c r="I67" t="n">
         <v>1462.921367450014</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.36</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>6.84</v>
+        <v>10.37</v>
       </c>
       <c r="M67" t="n">
         <v>2.23</v>
       </c>
       <c r="N67" t="n">
-        <v>4.68</v>
+        <v>6.14</v>
       </c>
       <c r="O67" t="n">
         <v>-2.01</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>13.21</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="H68" t="n">
-        <v>1561.6</v>
+        <v>1540.4</v>
       </c>
       <c r="I68" t="n">
         <v>1541.497172927833</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K68" t="n">
-        <v>6.05</v>
+        <v>4.61</v>
       </c>
       <c r="L68" t="n">
         <v>5.33</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>33</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9335,7 +10170,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.8</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="6">
@@ -9345,7 +10180,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -9355,7 +10190,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8">
@@ -9365,7 +10200,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -9375,7 +10210,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>77.5</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="10">
@@ -9385,7 +10220,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>97.8</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -9395,7 +10230,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -9405,7 +10240,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -9415,7 +10250,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.9</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="14">
@@ -9425,7 +10260,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.1</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="15">
@@ -9435,7 +10270,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.81</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="16">
@@ -9445,7 +10280,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.25</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="17">
@@ -9455,7 +10290,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>194.2</v>
+        <v>159.85</v>
       </c>
     </row>
     <row r="18">
@@ -9465,7 +10300,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46.3</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="19">
@@ -9475,7 +10310,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.710000000000001</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="20">
@@ -9485,7 +10320,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.71</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="21">
@@ -9505,7 +10340,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
@@ -9515,7 +10350,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24">
@@ -9525,7 +10360,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="25">
@@ -9545,7 +10380,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.85</v>
+        <v>6.32</v>
       </c>
     </row>
     <row r="27">
@@ -9565,7 +10400,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
